--- a/cds_files/UCF_CDS_2021-2022.xlsx
+++ b/cds_files/UCF_CDS_2021-2022.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.68</v>
+        <v>0.711</v>
       </c>
       <c r="C3" t="n">
-        <v>0.12</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.32</v>
+        <v>0.289</v>
       </c>
       <c r="C4" t="n">
-        <v>0.88</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +525,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
   </sheetData>
